--- a/files/SCSS calculators.xlsx
+++ b/files/SCSS calculators.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dianji/Desktop/S/Submission_GCA/R1 revision/submission/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dianji/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9788E06C-F37C-F14A-9F0F-2B5B6E5F668E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81BC0EBF-3FA4-5E4B-A851-89849644A600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15940" xr2:uid="{91727676-8232-884C-B32C-4101D9A5039A}"/>
+    <workbookView xWindow="780" yWindow="980" windowWidth="27640" windowHeight="15940" xr2:uid="{91727676-8232-884C-B32C-4101D9A5039A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="2" r:id="rId1"/>
-    <sheet name="SCSS calculator" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="150">
   <si>
     <t>Table S3. SCSS calculator and experiments used to test the new SCSS model.</t>
   </si>
@@ -530,40 +529,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Cr</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>O</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>5</t>
-    </r>
-  </si>
-  <si>
     <t>FeO*</t>
   </si>
   <si>
@@ -835,52 +800,45 @@
     <t>a. These experiments are from Mercury-relevant experiments but the starting materials did not contain Si metal. They have measured sulfide compositions. The rest of the experiments did not measure the sulfide composition, so we made an estimate. More details are given in the main text.</t>
   </si>
   <si>
-    <t>E-mail: dj56@rice.edu</t>
-  </si>
-  <si>
-    <t>Instructions</t>
-  </si>
-  <si>
-    <t>Supplement to: Sulfur inventory of the young lunar mantle constrained by experimental sulfide saturation of Chang’e-5 mare basalts and a new sulfur solubility model for silicate melts in equilibrium with sulfides of variable metal–sulfur ratio</t>
-  </si>
-  <si>
-    <t>Authors: Dian Ji and Rajdeep Dasgupta</t>
-  </si>
-  <si>
-    <t>1. Go to the sheet "SCSS calculator".</t>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">2. Input the required data for the part </t>
+      <t>Cr</t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>filled with green</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>.</t>
+      <t>2</t>
     </r>
-  </si>
-  <si>
-    <t>3. The parameters and SCSS values will be updated automatically.</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>3</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -945,31 +903,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1003,7 +936,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1056,10 +989,6 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1393,66 +1322,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8113D7BD-E329-4C4D-A1FB-D4BCF261CCF3}">
-  <dimension ref="A1:A14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="16384" width="10.83203125" style="19"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="20"/>
-    </row>
-    <row r="5" spans="1:1" ht="20" x14ac:dyDescent="0.2">
-      <c r="A5" s="18" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="20" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="20" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="20" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-    </row>
-    <row r="13" spans="1:1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
-    </row>
-    <row r="14" spans="1:1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A14" s="21"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F98282A-21DF-EB49-90BD-98F16E7E8B60}">
   <dimension ref="A1:DU47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -4066,7 +3935,7 @@
     </row>
     <row r="11" spans="1:125" ht="18" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="CT11" s="2">
         <v>0.03</v>
@@ -4131,7 +4000,7 @@
     </row>
     <row r="12" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B12" s="8">
         <v>10.92</v>
@@ -4508,7 +4377,7 @@
     </row>
     <row r="13" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B13" s="8">
         <v>0.17</v>
@@ -4670,7 +4539,7 @@
     </row>
     <row r="14" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B14" s="8">
         <v>22.39</v>
@@ -5047,7 +4916,7 @@
     </row>
     <row r="15" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B15" s="8">
         <v>5.96</v>
@@ -5424,7 +5293,7 @@
     </row>
     <row r="16" spans="1:125" ht="18" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B16" s="8">
         <v>0.97</v>
@@ -5699,7 +5568,7 @@
     </row>
     <row r="17" spans="1:125" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B17" s="8">
         <v>0.23</v>
@@ -5892,7 +5761,7 @@
     </row>
     <row r="18" spans="1:125" ht="18" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B18" s="8">
         <v>0.78</v>
@@ -6054,12 +5923,12 @@
     </row>
     <row r="19" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B20" s="8">
         <v>2220</v>
@@ -6437,7 +6306,7 @@
     </row>
     <row r="21" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B21" s="10">
         <f t="shared" ref="B21:BD21" si="0">SUM(B8:B18)+B19/10000+B20/10000</f>
@@ -6938,12 +6807,12 @@
     </row>
     <row r="23" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B24" s="10">
         <v>63.5</v>
@@ -7320,7 +7189,7 @@
     </row>
     <row r="25" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B25" s="10">
         <v>33.879199999999997</v>
@@ -7709,7 +7578,7 @@
     </row>
     <row r="26" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B26" s="10">
         <v>2.6208</v>
@@ -8090,7 +7959,7 @@
     </row>
     <row r="27" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
@@ -8225,7 +8094,7 @@
     </row>
     <row r="28" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
@@ -8354,7 +8223,7 @@
     </row>
     <row r="29" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B29" s="10">
         <f t="shared" ref="B29:BE29" si="6">SUM(B24:B28)</f>
@@ -8855,12 +8724,12 @@
     </row>
     <row r="31" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="1:125" ht="18" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B32" s="10">
         <f t="shared" ref="B32:BM32" si="8">B8/60.084/(B8/60.084+B9/79.865+B10/101.961*2+B11/151.986*2+B12/71.844+B13/70.937+B14/40.034+B15/56.077+B16/61.979*2+B17/94.195*2+B18/141.9445*2)</f>
@@ -9361,7 +9230,7 @@
     </row>
     <row r="33" spans="1:125" ht="18" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B33" s="10">
         <f t="shared" ref="B33:BM33" si="10">B9/79.865/(B8/60.084+B9/79.865+B10/101.961*2+B11/151.986*2+B12/71.844+B13/70.937+B14/40.034+B15/56.077+B16/61.979*2+B17/94.195*2+B18/141.9445*2)</f>
@@ -9862,7 +9731,7 @@
     </row>
     <row r="34" spans="1:125" ht="18" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B34" s="10">
         <f t="shared" ref="B34:BM34" si="12">B10/101.961*2/(B8/60.084+B9/79.865+B10/101.961*2+B11/151.986*2+B12/71.844+B13/70.937+B14/40.034+B15/56.077+B16/61.979*2+B17/94.195*2+B18/141.9445*2)</f>
@@ -10363,7 +10232,7 @@
     </row>
     <row r="35" spans="1:125" ht="18" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B35" s="10">
         <f t="shared" ref="B35:BM35" si="14">B15/56.077/(B8/60.084+B9/79.865+B10/101.961*2+B11/151.986*2+B12/71.844+B13/70.937+B14/40.034+B15/56.077+B16/61.979*2+B17/94.195*2+B18/141.9445*2)</f>
@@ -10864,7 +10733,7 @@
     </row>
     <row r="36" spans="1:125" ht="18" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B36" s="10">
         <f t="shared" ref="B36:BM36" si="16">B12/71.844/(B8/60.084+B9/79.865+B10/101.961*2+B11/151.986*2+B12/71.844+B13/70.937+B14/40.034+B15/56.077+B16/61.979*2+B17/94.195*2+B18/141.9445*2)</f>
@@ -11365,7 +11234,7 @@
     </row>
     <row r="37" spans="1:125" ht="18" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B37" s="10">
         <f t="shared" ref="B37:BM37" si="18">B14/40.034/(B8/60.084+B9/79.865+B10/101.961*2+B11/151.986*2+B12/71.844+B13/70.937+B14/40.034+B15/56.077+B16/61.979*2+B17/94.195*2+B18/141.9445*2)</f>
@@ -11866,7 +11735,7 @@
     </row>
     <row r="38" spans="1:125" ht="18" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B38" s="10">
         <f t="shared" ref="B38:BM38" si="20">IF((B25/32.06/(B24/55.845+B27/58.693+B28/63.546)*B24/55.845/(B24/55.845+B27/58.693+B28/63.546))&gt;1,1,(B25/32.06/(B24/55.845+B27/58.693+B28/63.546)*B24/55.845/(B24/55.845+B27/58.693+B28/63.546)))</f>
@@ -12367,7 +12236,7 @@
     </row>
     <row r="39" spans="1:125" ht="18" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B39" s="10">
         <f t="shared" ref="B39:BM39" si="22">IF((B25/32.06/(B24/55.845+B27/58.693+B28/63.546)*B27/58.693/(B24/55.845+B27/58.693+B28/63.546))&gt;1,1,(B25/32.06/(B24/55.845+B27/58.693+B28/63.546)*B27/58.693/(B24/55.845+B27/58.693+B28/63.546)))</f>
@@ -12868,7 +12737,7 @@
     </row>
     <row r="40" spans="1:125" ht="18" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B40" s="10">
         <f t="shared" ref="B40:BM40" si="24">IF((B25/32.06/(B24/55.845+B27/58.693+B28/63.546)*B28/63.546/(B24/55.845+B27/58.693+B28/63.546))&gt;1,1,(B25/32.06/(B24/55.845+B27/58.693+B28/63.546)*B28/63.546/(B24/55.845+B27/58.693+B28/63.546)))</f>
@@ -13369,7 +13238,7 @@
     </row>
     <row r="41" spans="1:125" ht="18" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B41" s="10">
         <f t="shared" ref="B41:BM41" si="26">IF((B24/55.845-(B25/32.06/(B24/55.845+B27/58.693+B28/63.546)*B24/55.845)-(B26/16/(B24/55.845+B27/58.693+B28/63.546)*B24/55.845))/(B24/55.845+B27/58.693+B28/63.546)&lt;0,0,(B24/55.845-(B25/32.06/(B24/55.845+B27/58.693+B28/63.546)*B24/55.845)-(B26/16/(B24/55.845+B27/58.693+B28/63.546)*B24/55.845))/(B24/55.845+B27/58.693+B28/63.546))</f>
@@ -13870,12 +13739,12 @@
     </row>
     <row r="43" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="44" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A44" s="16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B44" s="17">
         <f t="shared" ref="B44:BM44" si="28">EXP(13.81-5311/(B4+273.15)+0.17*B33+0.21*B35-4.42*B32-4.35*B34+4.3*B36-2.4*B37-9.7*B36*B33-315*B5/(B4+273.15)+LN(B38)-353/(B4+273.15)*B39*B39+2026/(B4+273.15)*B41*B41+3433/(B4+273.15)*B40*B40+3541/(B4+273.15)*B39*B41+14561/(B4+273.15)*B39*B40-9987/(B4+273.15)*B41*B40)</f>
@@ -14376,7 +14245,7 @@
     </row>
     <row r="45" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A45" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B45" s="17">
         <f t="shared" ref="B45:BM45" si="30">EXP(14.03-5417/(B4+273.15)-4.6*B32-4.49*B34+4.24*B36-2.53*B37-9.2*B36*B33-320*B5/(B4+273.15)+LN(B38)+2051/(B4+273.15)*B41*B41+16080/(B4+273.15)*B39*B40)</f>
@@ -14877,7 +14746,7 @@
     </row>
     <row r="47" spans="1:125" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
